--- a/stories/arbres/TREE-DIF-058.xlsx
+++ b/stories/arbres/TREE-DIF-058.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Léa est avec maman, dans la chambre. Léa a envie de jouer. maman est là, tout près. On va apprendre : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa écoute maman. Léa entend les mots : tailles différentes, jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Léa se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Léa va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Léa se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Léa se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; jouer. Léa respire. Léa retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Léa se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Léa va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Léa se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Léa se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; jouer. Léa respire. Léa retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Léa se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Léa va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Léa se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Léa se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; jouer. Léa respire. Léa retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-058.xlsx
+++ b/stories/arbres/TREE-DIF-058.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Léa est avec maman, dans la chambre. Léa a envie de jouer. maman est là, tout près. On va apprendre : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa écoute maman. Léa entend les mots : tailles différentes, jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; jouer. Léa respire. Léa retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Léa a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Léa rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Léa rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Léa rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Léa a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Léa rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Léa rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Léa rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Léa a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Léa rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Léa rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Léa rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; jouer. Léa respire. Léa retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Léa a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Léa rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Léa rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Léa rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Léa a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Léa rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Léa rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Léa rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Léa a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Léa rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Léa rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Léa rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; jouer. Léa respire. Léa retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Léa a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Léa rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Léa rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Léa rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Léa a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Léa rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Léa rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Léa rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Léa a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Léa répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Léa rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Léa rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Léa rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Léa a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Léa a entendu : tailles différentes, jouer ensemble. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-058.xlsx
+++ b/stories/arbres/TREE-DIF-058.xlsx
@@ -3280,17 +3280,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Les clochettes restent dans la paume de Chouchou. Je reste un peu. Une poussière reste collée aux cheveux. Une poussière dore les cheveux, sous l'abat-jour.</t>
+          <t>Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Les clochettes restent dans la paume de Chouchou. Je reste un peu. Tes cheveux sentent le bois. Une poussière dore les cheveux, sous l'abat-jour.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Les clochettes restent dans la paume de Chouchou. Je reste un peu. Une poussière reste collée aux cheveux. Une poussière dore les cheveux, sous l'abat-jour.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Les clochettes restent dans la paume de Chouchou. Je reste un peu. Tes cheveux sentent le bois. Une poussière dore les cheveux, sous l'abat-jour.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Les clochettes restent dans la paume de Chouchou. Je reste un peu. Une poussière reste collée aux cheveux. Une poussière dore les cheveux, sous l'abat-jour.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Les clochettes restent dans la paume de Chouchou. Je reste un peu. Tes cheveux sentent le bois. Une poussière dore les cheveux, sous l'abat-jour.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3435,7 +3435,7 @@
 maman|Vos voix sont devenues toutes petites.
 narrateur|Les clochettes restent dans la paume de Chouchou.
 copain|Je reste un peu.
-narrateur|Une poussière reste collée aux cheveux.
+enfant-f|Tes cheveux sentent le bois.
 narrateur|Une poussière dore les cheveux, sous l'abat-jour.</t>
         </is>
       </c>
@@ -5908,17 +5908,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Chouchou les pose contre la vitre. Les clochettes pèsent sur le loquet. Un rai jaune traverse le métal. Un rai jaune traverse le loquet.</t>
+          <t>Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Je les pose contre la vitre. Les clochettes pèsent sur le loquet. Le jaune de la rue les touche. Un rai jaune traverse le loquet.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Chouchou les pose contre la vitre. Les clochettes pèsent sur le loquet. Un rai jaune traverse le métal. Un rai jaune traverse le loquet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Je les pose contre la vitre. Les clochettes pèsent sur le loquet. Le jaune de la rue les touche. Un rai jaune traverse le loquet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Chouchou les pose contre la vitre. Les clochettes pèsent sur le loquet. Un rai jaune traverse le métal. Un rai jaune traverse le loquet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Je les pose contre la vitre. Les clochettes pèsent sur le loquet. Le jaune de la rue les touche. Un rai jaune traverse le loquet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -6061,9 +6061,9 @@
 copain|Tu nouais le bas.
 maman|Le carreau sent le soir, tout près.
 papa|La porte sonnera, demain.
-narrateur|Chouchou les pose contre la vitre.
+enfant-f|Je les pose contre la vitre.
 narrateur|Les clochettes pèsent sur le loquet.
-narrateur|Un rai jaune traverse le métal.
+copain|Le jaune de la rue les touche.
 narrateur|Un rai jaune traverse le loquet.</t>
         </is>
       </c>
@@ -8532,17 +8532,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Le ruban reste dans la paume de Chouchou. Je reste un peu. Une poussière reste collée aux cheveux. Le tabouret garde une mèche, dans l'ombre jaune.</t>
+          <t>Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Le ruban reste dans la paume de Chouchou. Je reste un peu. Une mèche à toi, sur le bois. Le tabouret garde une mèche, dans l'ombre jaune.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Le ruban reste dans la paume de Chouchou. Je reste un peu. Une poussière reste collée aux cheveux. Le tabouret garde une mèche, dans l'ombre jaune.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Le ruban reste dans la paume de Chouchou. Je reste un peu. Une mèche à toi, sur le bois. Le tabouret garde une mèche, dans l'ombre jaune.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Le ruban reste dans la paume de Chouchou. Je reste un peu. Une poussière reste collée aux cheveux. Le tabouret garde une mèche, dans l'ombre jaune.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. Le ruban reste dans la paume de Chouchou. Je reste un peu. Une mèche à toi, sur le bois. Le tabouret garde une mèche, dans l'ombre jaune.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8687,7 +8687,7 @@
 maman|Vos voix sont devenues toutes petites.
 narrateur|Le ruban reste dans la paume de Chouchou.
 copain|Je reste un peu.
-narrateur|Une poussière reste collée aux cheveux.
+enfant-f|Une mèche à toi, sur le bois.
 narrateur|Le tabouret garde une mèche, dans l'ombre jaune.</t>
         </is>
       </c>
@@ -11160,17 +11160,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Chouchou les pose contre la vitre. Le ruban rouge veille au loquet. Un rai jaune traverse le métal. Le loquet pèse, doré par la rue.</t>
+          <t>Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Je pose le rouge contre la vitre. Le ruban rouge veille au loquet. La rue le dore, un peu. Le loquet pèse, doré par la rue.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Chouchou les pose contre la vitre. Le ruban rouge veille au loquet. Un rai jaune traverse le métal. Le loquet pèse, doré par la rue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Je pose le rouge contre la vitre. Le ruban rouge veille au loquet. La rue le dore, un peu. Le loquet pèse, doré par la rue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Chouchou les pose contre la vitre. Le ruban rouge veille au loquet. Un rai jaune traverse le métal. Le loquet pèse, doré par la rue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Je pose le rouge contre la vitre. Le ruban rouge veille au loquet. La rue le dore, un peu. Le loquet pèse, doré par la rue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11313,9 +11313,9 @@
 copain|Tu nouais le bas.
 maman|Le carreau sent le soir, tout près.
 papa|La porte sonnera, demain.
-narrateur|Chouchou les pose contre la vitre.
+enfant-f|Je pose le rouge contre la vitre.
 narrateur|Le ruban rouge veille au loquet.
-narrateur|Un rai jaune traverse le métal.
+copain|La rue le dore, un peu.
 narrateur|Le loquet pèse, doré par la rue.</t>
         </is>
       </c>
@@ -11532,17 +11532,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Sur le rebord, deux paires de pieds se touchent. Tu as noué, d'en bas. Tes bras ont tenu le cadre. Chacun a fait sa part, à sa hauteur. Le satin du ruban sèche. Le ruban pose une ombre au plancher. Ça tinte trop, Chouchou. C'est pour ça. Deux paires de pieds se touchent, au rebord.</t>
+          <t>Sur le rebord, deux paires de pieds se touchent. Tu as noué, d'en bas. Tes bras ont tenu le cadre. Chacun a fait sa part, à sa hauteur. Le satin du ruban sèche. Le ruban pose une ombre au plancher. Ça tinte trop, Chouchou. C'est pour ça. Le satin laisse un trait rouge, au rebord.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le rebord, deux paires de pieds se touchent. Tu as noué, d'en bas. Tes bras ont tenu le cadre. Chacun a fait sa part, à sa hauteur. Le satin du ruban sèche. Le ruban pose une ombre au plancher. Ça tinte trop, Chouchou. C'est pour ça. Deux paires de pieds se touchent, au rebord.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le rebord, deux paires de pieds se touchent. Tu as noué, d'en bas. Tes bras ont tenu le cadre. Chacun a fait sa part, à sa hauteur. Le satin du ruban sèche. Le ruban pose une ombre au plancher. Ça tinte trop, Chouchou. C'est pour ça. Le satin laisse un trait rouge, au rebord.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le rebord, deux paires de pieds se touchent. Tu as noué, d'en bas. Tes bras ont tenu le cadre. Chacun a fait sa part, à sa hauteur. Le satin du ruban sèche. Le ruban pose une ombre au plancher. Ça tinte trop, Chouchou. C'est pour ça. Deux paires de pieds se touchent, au rebord.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le rebord, deux paires de pieds se touchent. Tu as noué, d'en bas. Tes bras ont tenu le cadre. Chacun a fait sa part, à sa hauteur. Le satin du ruban sèche. Le ruban pose une ombre au plancher. Ça tinte trop, Chouchou. C'est pour ça. Le satin laisse un trait rouge, au rebord.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11688,7 +11688,7 @@
 narrateur|Le ruban pose une ombre au plancher.
 copain|Ça tinte trop, Chouchou.
 enfant-f|C'est pour ça.
-narrateur|Deux paires de pieds se touchent, au rebord.</t>
+narrateur|Le satin laisse un trait rouge, au rebord.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -13784,17 +13784,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. L'anneau reste dans la paume de Chouchou. Je reste un peu. Une poussière reste collée aux cheveux. Le tabouret sent le bois, sous la lumière.</t>
+          <t>Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. L'anneau reste dans la paume de Chouchou. Je reste un peu. Il a pris ta poussière, Nino. Le tabouret sent le bois, sous la lumière.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. L'anneau reste dans la paume de Chouchou. Je reste un peu. Une poussière reste collée aux cheveux. Le tabouret sent le bois, sous la lumière.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. L'anneau reste dans la paume de Chouchou. Je reste un peu. Il a pris ta poussière, Nino. Le tabouret sent le bois, sous la lumière.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. L'anneau reste dans la paume de Chouchou. Je reste un peu. Une poussière reste collée aux cheveux. Le tabouret sent le bois, sous la lumière.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le tabouret, deux têtes se calment. Nino, tu l'as vue glisser. Oui, tout près de tes mains. Toi haute, lui qui noue, ça tenait. Vos voix sont devenues toutes petites. L'anneau reste dans la paume de Chouchou. Je reste un peu. Il a pris ta poussière, Nino. Le tabouret sent le bois, sous la lumière.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -13939,7 +13939,7 @@
 maman|Vos voix sont devenues toutes petites.
 narrateur|L'anneau reste dans la paume de Chouchou.
 copain|Je reste un peu.
-narrateur|Une poussière reste collée aux cheveux.
+enfant-f|Il a pris ta poussière, Nino.
 narrateur|Le tabouret sent le bois, sous la lumière.</t>
         </is>
       </c>
@@ -16412,17 +16412,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Chouchou les pose contre la vitre. L'anneau de bois veille au loquet. Un rai jaune traverse le métal. Les talons de Nino restent chauds, au loquet.</t>
+          <t>Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Je pose l'anneau contre la vitre. L'anneau de bois veille au loquet. Mes talons sont chauds, là. Les talons de Nino restent chauds, au loquet.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Chouchou les pose contre la vitre. L'anneau de bois veille au loquet. Un rai jaune traverse le métal. Les talons de Nino restent chauds, au loquet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Je pose l'anneau contre la vitre. L'anneau de bois veille au loquet. Mes talons sont chauds, là. Les talons de Nino restent chauds, au loquet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Chouchou les pose contre la vitre. L'anneau de bois veille au loquet. Un rai jaune traverse le métal. Les talons de Nino restent chauds, au loquet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les talons de Nino sont chauds. Tu as tenu le haut pour moi. Tu nouais le bas. Le carreau sent le soir, tout près. La porte sonnera, demain. Je pose l'anneau contre la vitre. L'anneau de bois veille au loquet. Mes talons sont chauds, là. Les talons de Nino restent chauds, au loquet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16565,9 +16565,9 @@
 copain|Tu nouais le bas.
 maman|Le carreau sent le soir, tout près.
 papa|La porte sonnera, demain.
-narrateur|Chouchou les pose contre la vitre.
+enfant-f|Je pose l'anneau contre la vitre.
 narrateur|L'anneau de bois veille au loquet.
-narrateur|Un rai jaune traverse le métal.
+copain|Mes talons sont chauds, là.
 narrateur|Les talons de Nino restent chauds, au loquet.</t>
         </is>
       </c>
@@ -17338,7 +17338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17451,6 +17451,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
